--- a/validation/results/annotation_workbook_onet29.xlsx
+++ b/validation/results/annotation_workbook_onet29.xlsx
@@ -1,21 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arcadauas-my.sharepoint.com/personal/einianma_arcada_fi/Documents/Documents/AI-on-Jobs/onet-task-isco-crosswalk/validation/results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_C265C1749BA873570B8D51F13DDC9350CF051FDD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB54BC3A-9057-4444-930B-E119F8CA15E7}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validation" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="598">
   <si>
     <t>task_id</t>
   </si>
@@ -1533,13 +1552,289 @@
   </si>
   <si>
     <t xml:space="preserve">  6=Agricultural  7=Craft  8=Operators  9=Elementary</t>
+  </si>
+  <si>
+    <t>Directing fish transfer to ponds/tanks is aquaculture production management. Next options: 1311 for general agricultural management; 6221 if the work is hands-on.</t>
+  </si>
+  <si>
+    <t>Cutting/shaping materials to measurement is core carpentry → 7115. Next options: 7522 for shop joinery/furniture; 9313 for helper-level work.</t>
+  </si>
+  <si>
+    <t>Inspecting/testing parts and systems of prefab/mobile homes is general building maintenance-repair, not woodworking → 7111. Next options: 7115 if occupation seen as carpentry trade; 7119 for prefab assembly focus.</t>
+  </si>
+  <si>
+    <t>Planning/implementing contaminated-site redevelopment for safety and compliance is environmental protection work → 2133. Next options: 1323 for project-management emphasis (off-crosswalk); 2142 for engineering-led redevelopment.</t>
+  </si>
+  <si>
+    <t>Basic cash handling/bookkeeping is one of many general office clerk duties → 4110. Next options: 4311 if coded by task (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Cleaning/dishwashing is a routine side duty of counter staff → 5246. Next options: 9411 if role seen as mainly food prep; 9412 if coded by task (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Sealing containers with glue/fasteners/hand tools is core hand-packing work → 9321. Next options: 8183 if on machine packaging lines.</t>
+  </si>
+  <si>
+    <t>Filing (signing off) regulatory compliance reports is part of managing the compliance function; specialists prepare, manager files → 1219. Next options: 2422 if role is specialist rather than managerial; 2619 for legal-compliance emphasis.</t>
+  </si>
+  <si>
+    <t>Participating in grading/sorting/post-harvest treatment is crop farm labourer work → 9211. Next options: 9214 for nursery/greenhouse settings; 6111 if skilled grower level.</t>
+  </si>
+  <si>
+    <t>Electric motor repairers adjusting part alignments/dimensions are electrical mechanics and fitters → 7412. Next options: 7233 for general machinery mechanics (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Arranging buying parties and soliciting sponsors is direct/party-plan selling → 5243. Next options: 5242 for sales demonstrators.</t>
+  </si>
+  <si>
+    <t>Moving/setting up mobile or prefab homes on lots is general small-dwelling building work → 7111. Next options: 7119 for prefab erection focus; 7115 if seen as carpentry trade.</t>
+  </si>
+  <si>
+    <t>Sorting mail into delivery sequence is core mail carrier work → 4412. Next options: 9621 for messengers/deliverers (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Ongoing prenatal health assessments are core midwifery work → 2222. Next options: 3222 for midwifery associate professionals; 2221 as broad nursing fallback.</t>
+  </si>
+  <si>
+    <t>Overseeing maintenance of wind field assets is operations management in electricity production (ISCO 1321 covers utilities) → 1321. Next options: 3122 for supervisor-level roles; 2151 for electrical engineering focus (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Copying/summarising recorded title documents is title-search work within legal associate professionals → 3411. Next options: 4415 for pure filing/copying clerks (off-crosswalk); 3334 for real estate emphasis.</t>
+  </si>
+  <si>
+    <t>Answering requests using directories is core telephone operator work → 4223. Next options: 4222 for contact-centre information clerks.</t>
+  </si>
+  <si>
+    <t>Inspecting buildings to scope weatherization work precedes installers' own insulation/sealing work → 7124. Next options: 3119 if role is mainly energy auditing; 3112 for building inspection (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Keeping kitchen areas, equipment and utensils clean is core dishwasher/kitchen helper work → 9412. Next options: 9112 for general cleaners.</t>
+  </si>
+  <si>
+    <t>Providing care, first aid and immunizations in schools/hospitals/industry is core registered nurse work → 2221. Next options: 3221 for nursing associate professionals (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Disinfecting equipment/supplies is routine housekeeping-cleaner work in establishments → 9112. Next options: 9111 for domestic household cleaners; 5153 for caretaker roles.</t>
+  </si>
+  <si>
+    <t>Scheduling appointments and maintaining calendars is core receptionist work → 4226. Next options: 4224 for hotel receptionists; 4222 for contact-centre clerks.</t>
+  </si>
+  <si>
+    <t>Counting cash drawers at shift start is core cashier work → 5230. Next options: 4211 for bank tellers (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Maintaining documentation of compliance activities is part of managing the compliance function → 1219. Next options: 2422 if role is specialist rather than managerial.</t>
+  </si>
+  <si>
+    <t>Recording product/packaging/order information is routine hand-packer record-keeping → 9321. Next options: 4321 if mainly stock clerking (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Emptying wastebaskets and transporting trash is routine housekeeping-cleaner work → 9112. Next options: 9111 for domestic cleaners; 9611 if refuse collection is the main job (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Looking up data to answer customer/public questions is receptionist and information clerk work → 4226. Next options: 4222 for contact-centre information clerks.</t>
+  </si>
+  <si>
+    <t>Recording crop information (pesticides, yields, costs) is a support task for crop farm labourers → 9211. Next options: 6111 if skilled grower level; 9214 for nursery/greenhouse settings.</t>
+  </si>
+  <si>
+    <t>Responding to regulatory agencies on product issues is part of managing the regulatory affairs function → 1219. Next options: 2422 if role is specialist rather than managerial; 2619 for legal emphasis.</t>
+  </si>
+  <si>
+    <t>Locking up and checking for hazards is a side duty of janitors/cleaners in buildings → 9112. Next options: 5153 for building caretakers; 5414 for security guards (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Preparing wind field operational budgets is operations management in electricity production → 1321. Next options: 1219 for general business administration management.</t>
+  </si>
+  <si>
+    <t>Controlling anaesthesia levels is done by nurse anaesthetists/anaesthesia nurses outside the US (AA role is US-only); coded to the European practitioner → 2221 (off-crosswalk). Next options: 2240 strict ISCO for anesthesiologist assistants; 2212 for anaesthesiologists.</t>
+  </si>
+  <si>
+    <t>Internationally, taking histories and recording exam results before/alongside the doctor is done by nurses; the PA role is rare outside a few countries → 2221 (off-crosswalk). Next options: 2240 strict ISCO for PAs/clinical officers; 2269 if restricted to crosswalk.</t>
+  </si>
+  <si>
+    <t>Tree trimmers/pruners internationally sit with forestry and related workers (tree surgeons, pruners); tool upkeep is a routine side task → 6210. Next options: 6113 for arborists in urban/landscape settings; 9215 for forestry labourers.</t>
+  </si>
+  <si>
+    <t>Measuring felled trees and bucking them into log lengths with chainsaws is core faller/forestry worker work → 6210. Next options: 9215 for forestry labourers; 8341 if mainly machine-based harvesting.</t>
+  </si>
+  <si>
+    <t>Post-sale client support to resolve problems is part of commercial sales representative work → 3322. Next options: 4222 if mainly customer-service; 2433/2434 for technical or ICT sales.</t>
+  </si>
+  <si>
+    <t>Harvesting, transplanting, potting and labelling plants is nursery/greenhouse work done internationally by horticultural labourers → 9214. Next options: 9211 for general crop labourers; 6113 if skilled nursery grower level.</t>
+  </si>
+  <si>
+    <t>Writing up orders or entering them into computers is routine door-to-door/direct sales work → 5243. Next options: 5244 for contact-centre sales; 4222 if mainly order-taking clerical work (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Internationally, investigating/interviewing suspected shoplifters is done by store detectives and security staff (ISCO 5414 includes store detectives) → 5414. Next options: 1219 for managerial loss-prevention framing; 3411 for private investigators (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Returning collected mail to the post office is core mail carrier work → 4412. Next options: 9621 for messengers/deliverers (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Completing and mailing bills, contracts and invoices is routine general office clerk work → 4110. Next options: 4311 for billing/accounting clerks (off-crosswalk); 4412 for mail-room clerks.</t>
+  </si>
+  <si>
+    <t>Examining land documents for registration and issuing rejections is land-registry legal-associate work in many countries (e.g. Rechtspfleger, land registry legal officers) → 3411. Borderline. Next options: 3359 for public registry officers (off-crosswalk); 2619 where registrars are lawyers.</t>
+  </si>
+  <si>
+    <t>Directing fish trapping, spawning, egg incubation and fry rearing is aquaculture production management → 1312. Next options: 6221 if hands-on aquaculture work; 1311 for general agricultural management.</t>
+  </si>
+  <si>
+    <t>Preparing claims, billing and complaint correspondence is core correspondence clerk work (ISCO 4419 includes correspondence clerks) → 4419. Next options: 4222 for customer-contact clerks (off-crosswalk); 4110 for general office clerks.</t>
+  </si>
+  <si>
+    <t>Repairing/rebuilding mechanical parts of electric motors and generators is electrical mechanic and fitter work → 7412. Next options: 7233 for general machinery mechanics (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Monitoring fetal growth via heartbeat, measurement and palpation is core midwifery work → 2222. Next options: 3222 for midwifery associate professionals; 2221 as broad nursing fallback.</t>
+  </si>
+  <si>
+    <t>Gathering and reviewing records to attach to correspondence is correspondence clerk work → 4419. Next options: 4415 for filing clerks; 4110 for general office clerks.</t>
+  </si>
+  <si>
+    <t>Supervising subcontractors/consultants on wind projects for quality and budget is construction/project management → 1323 (off-crosswalk). Next options: 1321 for operations-phase management; 2149 for engineering-led roles.</t>
+  </si>
+  <si>
+    <t>Contacting prospects and customers to discuss service needs is core commercial sales representative work → 3322. Next options: 5244 for contact-centre selling; 2433/2434 for technical/ICT sales.</t>
+  </si>
+  <si>
+    <t>Taking orders and writing tickets is core food service counter attendant work → 5246. Next options: 5131 for waiters; 5230 if mainly cashier work.</t>
+  </si>
+  <si>
+    <t>Investigating complaints and preparing regulatory submissions is hands-on regulatory affairs specialist work (specialist prepares, manager files) → 2422. Next options: 1219 for managerial oversight framing; 2619 for legal emphasis.</t>
+  </si>
+  <si>
+    <t>Administering loss-reduction, inventory-control and safety programmes is managerial programme administration → 1219. Next options: 5414 for security-led roles; 1324 for inventory/supply-chain management focus.</t>
+  </si>
+  <si>
+    <t>Training LP staff, retail managers and employees on loss control is part of managing the loss-prevention function → 1219. Next options: 5414 for security supervisors; 2424 for training professionals (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Teaching family members to give bedside care is home-based personal care work → 5322. Next options: 5321 for health care assistants in institutions.</t>
+  </si>
+  <si>
+    <t>Monitoring vital signs/medication under RN or physio direction in clients' homes is home-based personal care work → 5322. Next options: 5321 for institutional health care assistants; 3221 for nursing associates (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Monitoring maternal condition during labour is core midwifery work → 2222. Next options: 3222 for midwifery associate professionals; 2212 for obstetricians (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Determining and announcing fares with taximeters is core taxi driver work → 8322. Next options: 8331 for bus drivers.</t>
+  </si>
+  <si>
+    <t>Operating switchboard connections is core telephone switchboard operator work → 4223. Next options: 4222 for contact-centre clerks.</t>
+  </si>
+  <si>
+    <t>Reading blueprints to lay out work and determine materials is core carpentry → 7115. Next options: 3123 for construction supervisors; 7111 for general house builders.</t>
+  </si>
+  <si>
+    <t>Hoisting tools and lowering branches with ropes/rigging is tree-work within forestry and related workers → 6210. Next options: 9215 for forestry labourers/ground crew; 6113 for urban arborists.</t>
+  </si>
+  <si>
+    <t>Connecting water hoses and testing plumbing during mobile home set-up is part of multi-trade small-dwelling work → 7111. Next options: 7126 for plumbers; 7119 for prefab erection focus.</t>
+  </si>
+  <si>
+    <t>Assembling and fastening frameworks/props with hand tools is core carpentry → 7115. Next options: 7111 for house builders; 9313 for helper-level work.</t>
+  </si>
+  <si>
+    <t>Clearing brush, escape routes and saplings before felling is core faller/forestry worker work → 6210. Next options: 9215 for forestry labourers; 8341 if bulldozer-based.</t>
+  </si>
+  <si>
+    <t>Sweeping/scrubbing kitchen floors is a routine dishwasher/kitchen helper duty → 9412. Next options: 9112 for general cleaners.</t>
+  </si>
+  <si>
+    <t>Reading maps and following directions is core light delivery vehicle/van driver work → 8322. Next options: 8332 for heavy truck drivers; 9621 for delivery messengers (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Gathering and emptying trash is routine janitorial work in buildings → 9112. Next options: 9611 for refuse collectors (off-crosswalk); 5153 for caretakers.</t>
+  </si>
+  <si>
+    <t>Identifying environmental contamination sources is core environmental protection professional work → 2133. Next options: 3257 for environmental health inspectors; 2143 for environmental engineers.</t>
+  </si>
+  <si>
+    <t>Allocating resources and responding to infestations, drought and fire is farm management decision-making → 1311. Next options: 6130 for owner-operator mixed farmers (ISCO 6); 6111 for field crop growers.</t>
+  </si>
+  <si>
+    <t>Informing regular customers of new products and prices is sales work; route sales workers internationally do it as salespersons → 5243 (off-crosswalk). Next options: 8322 if coded by the driving (crosswalk only lists driver codes); 3322 for commercial sales reps.</t>
+  </si>
+  <si>
+    <t>Installing/sealing ducts and ventilation openings for energy efficiency is weatherization/insulation work → 7124. Next options: 7127 for HVAC mechanics (off-crosswalk); 7213 for sheet-metal duct work (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Reviewing exception reports and cash discrepancies for guideline adherence is managerial loss-control oversight → 1219. Next options: 5414 for security-led roles; 3313 for accounting associate review (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Driving taxis/private vehicles to transport passengers is core taxi driver work → 8322. Next options: 8321 for motorcycle taxis; 8331 for bus drivers.</t>
+  </si>
+  <si>
+    <t>Issuing receipts, refunds, credits and change is core cashier work → 5230. Next options: 5223 for shop sales assistants.</t>
+  </si>
+  <si>
+    <t>Stopping the saw, pulling the bar and retreating as the tree falls is core faller/forestry worker work → 6210. Next options: 9215 for forestry labourers.</t>
+  </si>
+  <si>
+    <t>Recording daily sales/delivery information, consistent with coding driver/sales workers as salespersons → 5243 (off-crosswalk). Next options: 8322 if coded by driving; 4321 for stock/delivery clerks (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Delivering mail along routes by foot or vehicle is core mail carrier work → 4412. Next options: 8322 if coded by driving; 9621 for messengers (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Operating a switchboard to answer/screen/forward calls and take messages is a standard receptionist duty → 4226. Next options: 4223 for dedicated switchboard operators (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Taking part in care-team case reviews on client needs is home-based personal care work → 5322. Next options: 5321 for institutional health care assistants; 3412 for social work associates.</t>
+  </si>
+  <si>
+    <t>Monitoring automated call systems and assisting callers is telephone switchboard operator work → 4223. Next options: 4222 for contact-centre clerks.</t>
+  </si>
+  <si>
+    <t>Estimating costs of environmental cleanup/remediation is environmental consultancy work → 2133. Next options: 2143 for environmental engineers; 2142/3112 for quantity surveying/cost estimation.</t>
+  </si>
+  <si>
+    <t>Measuring rpm, amperage and voltage with meters to diagnose motor faults is electrical mechanic and fitter work → 7412. Next options: 7411 for electricians; 3113 for electrical engineering technicians.</t>
+  </si>
+  <si>
+    <t>Administering blood products/fluids during anaesthesia is done internationally by anaesthesia nurses (AA role is US-only) → 2221 (off-crosswalk), consistent with row 132. Next options: 2240 strict ISCO for AAs; 2212 for anaesthesiologists.</t>
+  </si>
+  <si>
+    <t>Creating wind project plans (scope, schedules, costs, contingencies) is construction/project management → 1323 (off-crosswalk), consistent with row 157. Next options: 1321 for operations-phase management; 2149 for engineering-led planning.</t>
+  </si>
+  <si>
+    <t>Diagnostic physical examination is internationally performed by physicians (PA role is US-centric) → 2211. Next options: 2221 for nurse assessments/triage; 2240 strict ISCO for PAs.</t>
+  </si>
+  <si>
+    <t>Reassembling repaired motors to spec with hand tools and meters is electrical mechanic and fitter work → 7412, consistent with row 190. Next options: 8212 for factory motor assemblers; 7411 for electricians.</t>
+  </si>
+  <si>
+    <t>Managing wind project costs within budget is construction/project management → 1323 (off-crosswalk), consistent with rows 157/192. Next options: 1321 for operations-phase management; 1219 for general business management.</t>
+  </si>
+  <si>
+    <t>Following site safety rules and keeping a clean work area is a generic duty of the carpenter → 7115. Next options: 7119 for general building trades; 9313 for construction labourers.</t>
+  </si>
+  <si>
+    <t>Emergency CPR/BLS/ACLS in the anaesthesia setting is done internationally by anaesthesia nurses (AA role is US-only) → 2221 (off-crosswalk), consistent with rows 132/191. Next options: 2240 strict ISCO for AAs; 3258 for ambulance workers.</t>
+  </si>
+  <si>
+    <t>Pre-trip checks of fuel, oil, tyres, lights and brakes are routine duties of light delivery vehicle drivers → 8322. Next options: 8332 for heavy truck drivers; 7231 for vehicle mechanics (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Reporting needed building repairs to managers is part of cleaning/janitorial work → 9112, consistent with prior janitor rows. Next options: 5153 for building caretakers; 7133 for building cleaners.</t>
+  </si>
+  <si>
+    <t>Monitoring, recording and reporting patient symptoms is core nursing professional work → 2221. Next options: 3221 for nursing associate professionals (off-crosswalk); 5321 for health care assistants (off-crosswalk).</t>
+  </si>
+  <si>
+    <t>Removing panels, replacing structural frame members and sealing leaks in manufactured homes is carpentry repair work → 7115. Next options: 7119 for general building trades; 7126 for plumbing-related sealing.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1591,10 +1886,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1602,13 +1903,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1646,7 +1955,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1680,6 +1989,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1714,9 +2024,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1888,5256 +2199,5850 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CDB62E4E-E361-4DB0-8A8A-E8A1AF34ECE1}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;b5a0b36f-b135-4a9b-a069-e9a9bd102389&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="72.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2">
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>15849</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>4.38</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
+    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>15857</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>4.38</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>23901</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>4.24</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>15836</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F5">
-        <v>4.11</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="3">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>15834</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>4.07</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>15827</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>4.04</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
+    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>15822</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>4.51</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
+    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>15808</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F9">
-        <v>4.27</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" s="3">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="3" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
+    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>15809</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="3">
         <v>4.2</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11">
+    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>15800</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="3">
         <v>4.38</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
+    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>15807</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>4.29</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="3" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
+    <row r="13" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>15781</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>4.28</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>18026</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="3">
         <v>4.74</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="3" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15">
+    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>18037</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F15">
-        <v>4.61</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F15" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="3" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
+    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>18022</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F16">
-        <v>4.48</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F16" s="3">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>15645</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="3">
         <v>4.5</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
+    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>15650</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="3">
         <v>4.41</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>21088</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="3">
         <v>4.37</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20">
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>17466</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="3">
         <v>4.71</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>17479</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F21">
-        <v>4.69</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="F21" s="3">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22">
+    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>17486</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="3">
         <v>4.62</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23">
+    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>1841</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="3">
         <v>4.74</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24">
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>20413</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="3">
         <v>4.7</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="3" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25">
+    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>1839</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F25">
-        <v>4.69</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F25" s="3">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26">
+    <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>23222</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G26" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27">
+    <row r="27" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>23223</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G27" t="s">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="3" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28">
+    <row r="28" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>23224</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G28" t="s">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="3" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29">
+    <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>9231</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <v>4.75</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="3" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30">
+    <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>9234</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <v>4.59</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="3" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31">
+    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>9235</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F31">
-        <v>4.56</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="F31" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32">
+    <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>17310</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F32">
-        <v>4.9</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="F32" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="3" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33">
+    <row r="33" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>17305</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <v>4.82</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
-      <c r="A34">
+    <row r="34" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>17301</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="3">
         <v>4.68</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
-      <c r="A35">
+    <row r="35" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>4075</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F35">
-        <v>4.94</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="F35" s="3">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36">
+    <row r="36" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>4074</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="3">
         <v>4.92</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37">
+    <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>4078</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <v>4.92</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38">
+    <row r="38" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>11281</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="3">
         <v>4.43</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
-      <c r="A39">
+    <row r="39" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>11276</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F39">
-        <v>4.11</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="F39" s="3">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="3" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40">
+    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>11273</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="3">
         <v>3.99</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="3" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41">
+    <row r="41" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>830</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F41">
-        <v>4.56</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="F41" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="3" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42">
+    <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>827</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <v>4.34</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="3" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43">
+    <row r="43" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>826</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="3">
         <v>4.28</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44">
+    <row r="44" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>13246</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F44">
-        <v>4.61</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="F44" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45">
+    <row r="45" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>13256</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <v>4.54</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="3" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46">
+    <row r="46" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>13247</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="3">
         <v>4.45</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="3" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47">
+    <row r="47" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>744</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="3">
         <v>4.74</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48">
+    <row r="48" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>747</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F48">
-        <v>4.69</v>
-      </c>
-      <c r="G48" t="s">
+      <c r="F48" s="3">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="3" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49">
+    <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>745</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F49">
-        <v>4.64</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="F49" s="3">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50">
+    <row r="50" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>2400</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="3">
         <v>4.75</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51">
+    <row r="51" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>2403</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <v>4.7</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="3" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52">
+    <row r="52" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>2411</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="3">
         <v>4.67</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53">
+    <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>13233</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="3">
         <v>4.7</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54">
+    <row r="54" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>13238</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="3">
         <v>4.41</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="3" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55">
+    <row r="55" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>13231</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="3">
         <v>4.32</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56">
+    <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>2371</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F56">
-        <v>4.65</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="F56" s="3">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="3" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57">
+    <row r="57" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>2370</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F57">
-        <v>4.65</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="F57" s="3">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="3" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58">
+    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>2378</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F58">
-        <v>4.56</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="F58" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59">
+    <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>23099</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F59">
-        <v>4.64</v>
-      </c>
-      <c r="G59" t="s">
+      <c r="F59" s="3">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="3" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60">
+    <row r="60" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>23101</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="3">
         <v>4.63</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="3" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61">
+    <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>23100</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="3">
         <v>4.63</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
-      <c r="A62">
+    <row r="62" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>21370</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="3">
         <v>4.45</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
-      <c r="A63">
+    <row r="63" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>21371</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F63">
-        <v>4.36</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="F63" s="3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="3" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
-      <c r="A64">
+    <row r="64" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>21372</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <v>4.2</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="3" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
-      <c r="A65">
+    <row r="65" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>13120</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F65">
-        <v>4.39</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="F65" s="3">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="3" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
-      <c r="A66">
+    <row r="66" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>13113</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="3">
         <v>4.37</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="3" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67">
+    <row r="67" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>13116</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="3">
         <v>4.33</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="3" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68">
+    <row r="68" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>23376</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="3">
         <v>4.17</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69">
+    <row r="69" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>23387</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="3">
         <v>4.12</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="3" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70">
+    <row r="70" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>23379</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="3">
         <v>4.09</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="3" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71">
+    <row r="71" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>13484</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="3">
         <v>4.67</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72">
+    <row r="72" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>13485</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F72">
-        <v>4.65</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="F72" s="3">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="G72" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="3" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
-      <c r="A73">
+    <row r="73" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>13486</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F73">
-        <v>4.61</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="F73" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G73" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I73" s="3" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74">
+    <row r="74" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>21204</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F74">
-        <v>4.6</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="F74" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="I74" t="s">
+      <c r="I74" s="3" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75">
+    <row r="75" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>21205</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="3">
         <v>4.41</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G75" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I75" s="3" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76">
+    <row r="76" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>17789</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="3">
         <v>4.29</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I76" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
-      <c r="A77">
+    <row r="77" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>13878</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F77">
-        <v>4.44</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="F77" s="3">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I77" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
-      <c r="A78">
+    <row r="78" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>13879</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F78">
-        <v>4.36</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="F78" s="3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I78" s="3" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
-      <c r="A79">
+    <row r="79" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>13880</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="3">
         <v>4.04</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G79" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I79" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
-      <c r="A80">
+    <row r="80" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>11696</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="3">
         <v>4.53</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G80" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I80" s="3" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
-      <c r="A81">
+    <row r="81" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>11713</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="3">
         <v>4.25</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81" s="3" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
-      <c r="A82">
+    <row r="82" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>11690</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F82">
-        <v>4.23</v>
-      </c>
-      <c r="G82" t="s">
+      <c r="F82" s="3">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G82" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I82" s="3" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
-      <c r="A83">
+    <row r="83" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>23430</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="3">
         <v>4.67</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I83" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
-      <c r="A84">
+    <row r="84" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>23432</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="3">
         <v>4.62</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I84" s="3" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
-      <c r="A85">
+    <row r="85" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
         <v>23443</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="3">
         <v>4.41</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="I85" t="s">
+      <c r="I85" s="3" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
-      <c r="A86">
+    <row r="86" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
         <v>23758</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G86" t="s">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I86" s="3" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
-      <c r="A87">
+    <row r="87" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
         <v>23759</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G87" t="s">
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I87" t="s">
+      <c r="I87" s="3" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
-      <c r="A88">
+    <row r="88" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
         <v>23760</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G88" t="s">
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I88" t="s">
+      <c r="I88" s="3" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
-      <c r="A89">
+    <row r="89" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
         <v>3158</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="3">
         <v>4.32</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I89" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
-      <c r="A90">
+    <row r="90" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
         <v>3163</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="3">
         <v>4.17</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I90" t="s">
+      <c r="I90" s="3" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
-      <c r="A91">
+    <row r="91" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
         <v>3159</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F91">
-        <v>4.1</v>
-      </c>
-      <c r="G91" t="s">
+      <c r="F91" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G91" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="I91" t="s">
+      <c r="I91" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
-      <c r="A92">
+    <row r="92" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
         <v>8615</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="3">
         <v>4.83</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I92" t="s">
+      <c r="I92" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
-      <c r="A93">
+    <row r="93" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
         <v>8617</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="3">
         <v>4.79</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I93" s="3" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
-      <c r="A94">
+    <row r="94" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>8620</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="3">
         <v>4.76</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I94" s="3" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
-      <c r="A95">
+    <row r="95" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>20906</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F95">
-        <v>4.77</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="F95" s="3">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="G95" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I95" t="s">
+      <c r="I95" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
-      <c r="A96">
+    <row r="96" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
         <v>11341</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="3">
         <v>4.7</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G96" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I96" t="s">
+      <c r="I96" s="3" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
-      <c r="A97">
+    <row r="97" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
         <v>11344</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="3">
         <v>4.68</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I97" t="s">
+      <c r="I97" s="3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
-      <c r="A98">
+    <row r="98" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>11186</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F98">
-        <v>4.77</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="F98" s="3">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="G98" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I98" t="s">
+      <c r="I98" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
-      <c r="A99">
+    <row r="99" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
         <v>11187</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="3">
         <v>4.5</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G99" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I99" t="s">
+      <c r="I99" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100">
+    <row r="100" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
         <v>11192</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="3">
         <v>4.45</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I100" t="s">
+      <c r="I100" s="3" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
-      <c r="A101">
+    <row r="101" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
         <v>21216</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="3">
         <v>4.5</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102">
+    <row r="102" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
         <v>3212</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F102">
-        <v>4.4</v>
-      </c>
-      <c r="G102" t="s">
+      <c r="F102" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G102" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I102" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
-      <c r="A103">
+    <row r="103" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
         <v>3215</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="3">
         <v>4.28</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I103" s="3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
-      <c r="A104">
+    <row r="104" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
         <v>9564</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="3">
         <v>4.42</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I104" t="s">
+      <c r="I104" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
-      <c r="A105">
+    <row r="105" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
         <v>9560</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="3">
         <v>4.38</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I105" t="s">
+      <c r="I105" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
-      <c r="A106">
+    <row r="106" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
         <v>9561</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="3">
         <v>4.34</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G106" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I106" t="s">
+      <c r="I106" s="3" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
-      <c r="A107">
+    <row r="107" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
         <v>9538</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="3">
         <v>4.24</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I107" t="s">
+      <c r="I107" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
-      <c r="A108">
+    <row r="108" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
         <v>9539</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F108">
-        <v>4.23</v>
-      </c>
-      <c r="G108" t="s">
+      <c r="F108" s="3">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G108" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I108" t="s">
+      <c r="I108" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
-      <c r="A109">
+    <row r="109" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
         <v>9540</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="3">
         <v>4.21</v>
       </c>
-      <c r="G109" t="s">
+      <c r="G109" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="I109" t="s">
+      <c r="I109" s="3" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
-      <c r="A110">
+    <row r="110" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
         <v>21373</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F110">
-        <v>4.11</v>
-      </c>
-      <c r="G110" t="s">
+      <c r="F110" s="3">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="G110" s="3" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="111" spans="1:9">
-      <c r="A111">
+      <c r="H110" s="3">
+        <v>1312</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
         <v>4076</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="3">
         <v>4.92</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G111" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="A112">
+      <c r="H111" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
         <v>23433</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F112">
-        <v>4.36</v>
-      </c>
-      <c r="G112" t="s">
+      <c r="F112" s="3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="G112" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113">
+      <c r="H112" s="3">
+        <v>7115</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
         <v>13880</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="3">
         <v>4.04</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G113" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114">
+      <c r="H113" s="3">
+        <v>7111</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
         <v>15848</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="3">
         <v>4.21</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115">
+      <c r="H114" s="3">
+        <v>2133</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
         <v>825</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F115">
-        <v>4.14</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="F115" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="G115" s="3" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116">
+      <c r="H115" s="3">
+        <v>4110</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
         <v>23102</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="3">
         <v>4.58</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G116" s="3" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117">
+      <c r="H116" s="3">
+        <v>5246</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
         <v>3216</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F117">
-        <v>4.23</v>
-      </c>
-      <c r="G117" t="s">
+      <c r="F117" s="3">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G117" s="3" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118">
+      <c r="H117" s="3">
+        <v>9321</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
         <v>15653</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F118">
-        <v>4.27</v>
-      </c>
-      <c r="G118" t="s">
+      <c r="F118" s="3">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G118" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119">
+      <c r="H118" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
         <v>23392</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="3">
         <v>4.03</v>
       </c>
-      <c r="G119" t="s">
+      <c r="G119" s="3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120">
+      <c r="H119" s="3">
+        <v>9211</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
         <v>11713</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="3">
         <v>4.25</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G120" s="3" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121">
+      <c r="H120" s="3">
+        <v>7412</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>13235</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="3">
         <v>4.22</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G121" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122">
+      <c r="H121" s="3">
+        <v>5243</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
         <v>13879</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F122">
-        <v>4.36</v>
-      </c>
-      <c r="G122" t="s">
+      <c r="F122" s="3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="G122" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123">
+      <c r="H122" s="3">
+        <v>7111</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
         <v>11342</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="3">
         <v>4.63</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124">
+      <c r="H123" s="3">
+        <v>4412</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
         <v>17472</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F124">
-        <v>4.61</v>
-      </c>
-      <c r="G124" t="s">
+      <c r="F124" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G124" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125">
+      <c r="H124" s="3">
+        <v>2222</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
         <v>15823</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="3">
         <v>4.12</v>
       </c>
-      <c r="G125" t="s">
+      <c r="G125" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126">
+      <c r="H125" s="3">
+        <v>1321</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
         <v>9233</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="3">
         <v>4.51</v>
       </c>
-      <c r="G126" t="s">
+      <c r="G126" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127">
+      <c r="H126" s="3">
+        <v>3411</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
         <v>13243</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="3">
         <v>4.22</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G127" s="3" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128">
+      <c r="H127" s="3">
+        <v>4223</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
         <v>17787</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F128">
-        <v>4.19</v>
-      </c>
-      <c r="G128" t="s">
+      <c r="F128" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="G128" s="3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129">
+      <c r="H128" s="3">
+        <v>7124</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
         <v>11188</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="3">
         <v>4.18</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="3" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130">
+      <c r="H129" s="3">
+        <v>9412</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
         <v>1855</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F130">
-        <v>4.56</v>
-      </c>
-      <c r="G130" t="s">
+      <c r="F130" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G130" s="3" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131">
+      <c r="H130" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
         <v>9570</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="3">
         <v>4.29</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="3" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132">
+      <c r="H131" s="3">
+        <v>9112</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
         <v>17310</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F132">
-        <v>4.9</v>
-      </c>
-      <c r="G132" t="s">
+      <c r="F132" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G132" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133">
+      <c r="H132" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
         <v>751</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F133">
-        <v>4.4</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="F133" s="3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G133" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134">
+      <c r="H133" s="3">
+        <v>4226</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
         <v>2402</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="F134">
-        <v>4.6</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="F134" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G134" s="3" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135">
+      <c r="H134" s="3">
+        <v>5230</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
         <v>15638</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="3">
         <v>4.24</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G135" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136">
+      <c r="H135" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
         <v>3214</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="3">
         <v>4.24</v>
       </c>
-      <c r="G136" t="s">
+      <c r="G136" s="3" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137">
+      <c r="H136" s="3">
+        <v>9321</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
         <v>9562</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="3">
         <v>4.2</v>
       </c>
-      <c r="G137" t="s">
+      <c r="G137" s="3" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138">
+      <c r="H137" s="3">
+        <v>9112</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
         <v>752</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="3">
         <v>4.22</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G138" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139">
+      <c r="H138" s="3">
+        <v>4226</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
         <v>23387</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="3">
         <v>4.12</v>
       </c>
-      <c r="G139" t="s">
+      <c r="G139" s="3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140">
+      <c r="H139" s="3">
+        <v>9211</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
         <v>18035</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F140">
+      <c r="F140" s="3">
         <v>4.43</v>
       </c>
-      <c r="G140" t="s">
+      <c r="G140" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141">
+      <c r="H140" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
         <v>20590</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="3">
         <v>4.2</v>
       </c>
-      <c r="G141" t="s">
+      <c r="G141" s="3" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142">
+      <c r="H141" s="3">
+        <v>9112</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
         <v>15821</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="3">
         <v>4.09</v>
       </c>
-      <c r="G142" t="s">
+      <c r="G142" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143">
+      <c r="H142" s="3">
+        <v>1321</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
         <v>13115</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F143">
+      <c r="F143" s="3">
         <v>4.33</v>
       </c>
-      <c r="G143" t="s">
+      <c r="G143" s="3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144">
+      <c r="H143" s="3">
+        <v>6210</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
         <v>13488</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="3">
         <v>4.46</v>
       </c>
-      <c r="G144" t="s">
+      <c r="G144" s="3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145">
+      <c r="H144" s="3">
+        <v>6210</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
         <v>23225</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G145" t="s">
+      <c r="F145" s="3"/>
+      <c r="G145" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146">
+      <c r="H145" s="3">
+        <v>3322</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
         <v>23370</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="3">
         <v>4.03</v>
       </c>
-      <c r="G146" t="s">
+      <c r="G146" s="3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147">
+      <c r="H146" s="3">
+        <v>9214</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
         <v>13232</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="3">
         <v>4.32</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G147" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148">
+      <c r="H147" s="3">
+        <v>5243</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
         <v>15786</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="F148">
+      <c r="F148" s="3">
         <v>4.2</v>
       </c>
-      <c r="G148" t="s">
+      <c r="G148" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149">
+      <c r="H148" s="3">
+        <v>5414</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
         <v>11344</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="3">
         <v>4.68</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G149" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150">
+      <c r="H149" s="3">
+        <v>4412</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
         <v>829</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F150">
-        <v>4.11</v>
-      </c>
-      <c r="G150" t="s">
+      <c r="F150" s="3">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="G150" s="3" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151">
+      <c r="H150" s="3">
+        <v>4110</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
         <v>9236</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="3">
         <v>4.46</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152">
+      <c r="H151" s="3">
+        <v>3411</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
         <v>21372</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D152" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F152">
+      <c r="F152" s="3">
         <v>4.2</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="3" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153">
+      <c r="H152" s="3">
+        <v>1312</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
         <v>11270</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D153" t="s">
+      <c r="D153" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="3">
         <v>3.96</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G153" s="3" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154">
+      <c r="H153" s="3">
+        <v>4419</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
         <v>11692</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F154">
+      <c r="F154" s="3">
         <v>4.2</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G154" s="3" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155">
+      <c r="H154" s="3">
+        <v>7412</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
         <v>17481</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D155" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F155">
-        <v>4.6</v>
-      </c>
-      <c r="G155" t="s">
+      <c r="F155" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G155" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156">
+      <c r="H155" s="3">
+        <v>2222</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A156" s="3">
         <v>11277</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D156" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F156">
+      <c r="F156" s="3">
         <v>3.97</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G156" s="3" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157">
+      <c r="H156" s="3">
+        <v>4419</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
         <v>15824</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C157" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D157" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="3">
         <v>3.95</v>
       </c>
-      <c r="G157" t="s">
+      <c r="G157" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158">
+      <c r="H157" s="3">
+        <v>1323</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
         <v>23226</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D158" t="s">
+      <c r="D158" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="G158" t="s">
+      <c r="F158" s="3"/>
+      <c r="G158" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159">
+      <c r="H158" s="3">
+        <v>3322</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
         <v>23119</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D159" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="3">
         <v>4.59</v>
       </c>
-      <c r="G159" t="s">
+      <c r="G159" s="3" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160">
+      <c r="H159" s="3">
+        <v>5246</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A160" s="3">
         <v>18029</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D160" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="3">
         <v>4.47</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G160" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161">
+      <c r="H160" s="3">
+        <v>2422</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
         <v>15807</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D161" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="3">
         <v>4.29</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G161" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162">
+      <c r="H161" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A162" s="3">
         <v>15791</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D162" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="3">
         <v>4.24</v>
       </c>
-      <c r="G162" t="s">
+      <c r="G162" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163">
+      <c r="H162" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A163" s="3">
         <v>2378</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D163" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F163">
-        <v>4.56</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="F163" s="3">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="G163" s="3" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164">
+      <c r="H163" s="3">
+        <v>5322</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A164" s="3">
         <v>2369</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D164" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="3">
         <v>4.46</v>
       </c>
-      <c r="G164" t="s">
+      <c r="G164" s="3" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165">
+      <c r="H164" s="3">
+        <v>5322</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A165" s="3">
         <v>17466</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D165" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="3">
         <v>4.71</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G165" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166">
+      <c r="H165" s="3">
+        <v>2222</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A166" s="3">
         <v>23761</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G166" t="s">
+      <c r="F166" s="3"/>
+      <c r="G166" s="3" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167">
+      <c r="H166" s="3">
+        <v>8322</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="3">
         <v>13246</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D167" t="s">
+      <c r="D167" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F167">
-        <v>4.61</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="F167" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G167" s="3" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168">
+      <c r="H167" s="3">
+        <v>4223</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="3">
         <v>23431</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F168">
-        <v>4.36</v>
-      </c>
-      <c r="G168" t="s">
+      <c r="F168" s="3">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="G168" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169">
+      <c r="H168" s="3">
+        <v>7115</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A169" s="3">
         <v>13119</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D169" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="3">
         <v>4.25</v>
       </c>
-      <c r="G169" t="s">
+      <c r="G169" s="3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170">
+      <c r="H169" s="3">
+        <v>6210</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A170" s="3">
         <v>13881</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E170" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="3">
         <v>4</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G170" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171">
+      <c r="H170" s="3">
+        <v>7111</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A171" s="3">
         <v>23443</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="3">
         <v>4.41</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172">
+      <c r="H171" s="3">
+        <v>7115</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A172" s="3">
         <v>13487</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C172" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="F172">
+      <c r="F172" s="3">
         <v>4.55</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G172" s="3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173">
+      <c r="H172" s="3">
+        <v>6210</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A173" s="3">
         <v>11190</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F173">
-        <v>4.31</v>
-      </c>
-      <c r="G173" t="s">
+      <c r="F173" s="3">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="G173" s="3" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174">
+      <c r="H173" s="3">
+        <v>9412</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A174" s="3">
         <v>8623</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="3">
         <v>4.7</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G174" s="3" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175">
+      <c r="H174" s="3">
+        <v>8322</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="3">
         <v>9539</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D175" t="s">
+      <c r="D175" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F175">
-        <v>4.23</v>
-      </c>
-      <c r="G175" t="s">
+      <c r="F175" s="3">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G175" s="3" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176">
+      <c r="H175" s="3">
+        <v>9112</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A176" s="3">
         <v>15849</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="3">
         <v>4.38</v>
       </c>
-      <c r="G176" t="s">
+      <c r="G176" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177">
+      <c r="H176" s="3">
+        <v>2133</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A177" s="3">
         <v>21374</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F177">
-        <v>4.1</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="F177" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G177" s="3" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178">
+      <c r="H177" s="3">
+        <v>1311</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A178" s="3">
         <v>3156</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F178">
-        <v>4.06</v>
-      </c>
-      <c r="G178" t="s">
+      <c r="F178" s="3">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="G178" s="3" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179">
+      <c r="H178" s="3">
+        <v>5243</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A179" s="3">
         <v>17792</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F179">
+      <c r="F179" s="3">
         <v>4.29</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180">
+      <c r="H179" s="3">
+        <v>7124</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A180" s="3">
         <v>15781</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="3">
         <v>4.28</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G180" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181">
+      <c r="H180" s="3">
+        <v>1219</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A181" s="3">
         <v>23762</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G181" t="s">
+      <c r="F181" s="3"/>
+      <c r="G181" s="3" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182">
+      <c r="H181" s="3">
+        <v>8322</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A182" s="3">
         <v>2401</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="3">
         <v>4.66</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G182" s="3" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183">
+      <c r="H182" s="3">
+        <v>5230</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
         <v>13484</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="3">
         <v>4.67</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G183" s="3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="184" spans="1:7">
-      <c r="A184">
+      <c r="H183" s="3">
+        <v>6210</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
         <v>3161</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="3">
         <v>4.04</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="3" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185">
+      <c r="H184" s="3">
+        <v>5243</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A185" s="3">
         <v>11343</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="3">
         <v>4.58</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G185" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="186" spans="1:7">
-      <c r="A186">
+      <c r="H185" s="3">
+        <v>4412</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A186" s="3">
         <v>744</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C186" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="3">
         <v>4.74</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G186" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="187" spans="1:7">
-      <c r="A187">
+      <c r="H186" s="3">
+        <v>4226</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A187" s="3">
         <v>2376</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="3">
         <v>4.45</v>
       </c>
-      <c r="G187" t="s">
+      <c r="G187" s="3" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="188" spans="1:7">
-      <c r="A188">
+      <c r="H187" s="3">
+        <v>5322</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A188" s="3">
         <v>13250</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F188">
-        <v>4.19</v>
-      </c>
-      <c r="G188" t="s">
+      <c r="F188" s="3">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="G188" s="3" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="189" spans="1:7">
-      <c r="A189">
+      <c r="H188" s="3">
+        <v>4223</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A189" s="3">
         <v>15850</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="3">
         <v>4.18</v>
       </c>
-      <c r="G189" t="s">
+      <c r="G189" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="190" spans="1:7">
-      <c r="A190">
+      <c r="H189" s="3">
+        <v>2133</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A190" s="3">
         <v>11688</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="3">
         <v>4.21</v>
       </c>
-      <c r="G190" t="s">
+      <c r="G190" s="3" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="191" spans="1:7">
-      <c r="A191">
+      <c r="H190" s="3">
+        <v>7412</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A191" s="3">
         <v>17309</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D191" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="3">
         <v>4.67</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G191" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="192" spans="1:7">
-      <c r="A192">
+      <c r="H191" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A192" s="3">
         <v>15838</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="3">
         <v>3.99</v>
       </c>
-      <c r="G192" t="s">
+      <c r="G192" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="193" spans="1:7">
-      <c r="A193">
+      <c r="H192" s="3">
+        <v>1323</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A193" s="3">
         <v>4073</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="3">
         <v>4.92</v>
       </c>
-      <c r="G193" t="s">
+      <c r="G193" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194">
+      <c r="H193" s="3">
+        <v>2211</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A194" s="3">
         <v>11690</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C194" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F194">
-        <v>4.23</v>
-      </c>
-      <c r="G194" t="s">
+      <c r="F194" s="3">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="G194" s="3" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195">
+      <c r="H194" s="3">
+        <v>7412</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A195" s="3">
         <v>15834</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C195" t="s">
+      <c r="C195" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="3">
         <v>4.07</v>
       </c>
-      <c r="G195" t="s">
+      <c r="G195" s="3" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196">
+      <c r="H195" s="3">
+        <v>1323</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A196" s="3">
         <v>23430</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F196">
+      <c r="F196" s="3">
         <v>4.67</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G196" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197">
+      <c r="H196" s="3">
+        <v>7115</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A197" s="3">
         <v>17302</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="3">
         <v>4.68</v>
       </c>
-      <c r="G197" t="s">
+      <c r="G197" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198">
+      <c r="H197" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A198" s="3">
         <v>8616</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F198">
+      <c r="F198" s="3">
         <v>4.72</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G198" s="3" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199">
+      <c r="H198" s="3">
+        <v>8322</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A199" s="3">
         <v>9544</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="3">
         <v>4.2</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="3" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200">
+      <c r="H199" s="3">
+        <v>9112</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A200" s="3">
         <v>1840</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D200" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F200">
-        <v>4.61</v>
-      </c>
-      <c r="G200" t="s">
+      <c r="F200" s="3">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="G200" s="3" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201">
+      <c r="H200" s="3">
+        <v>2221</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A201" s="3">
         <v>13882</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="3">
         <v>3.81</v>
       </c>
-      <c r="G201" t="s">
+      <c r="G201" s="3" t="s">
         <v>310</v>
+      </c>
+      <c r="H201" s="3">
+        <v>7115</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -7146,226 +8051,226 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>505</v>
       </c>
@@ -7373,4 +8278,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{86080f64-b23d-4f93-8c43-e65f2588b9c3}" enabled="0" method="" siteId="{86080f64-b23d-4f93-8c43-e65f2588b9c3}" removed="1"/>
+</clbl:labelList>
 </file>